--- a/sampleprojects/TaxReturn/excel/states/MI.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MI.xlsx
@@ -72,7 +72,7 @@
     <t>MI exemptions = $5,800 x (taxpayers + dependents); tax = 4.25% x max(AGI - exemptions, 0)</t>
   </si>
   <si>
-    <t>set result.mi_total_exemption = (length of job.taxpayers + length of job.dependents) * mi_exemption_single; set result.mi_taxable_income = the maximum of (result.agi - result.mi_total_exemption) and 0.0; set result.mi_state_tax = result.mi_taxable_income * mi_tax_rate; add "  MI exemptions ($5,800 per person): $" + result.mi_total_exemption to job.audit_trail; add "  MI state tax (4.25%): $" + result.mi_state_tax to job.audit_trail</t>
+    <t>set result.mi_total_exemption = (length of job.taxpayers + length of job.dependents) * mi_exemption_single; set result.mi_taxable_income = the maximum of (result.state_calc_agi - result.mi_total_exemption) and 0.0; set result.mi_state_tax = result.mi_taxable_income * mi_tax_rate; add "  MI exemptions ($5,800 per person): $" + result.mi_total_exemption to job.audit_trail; add "  MI state tax (4.25%): $" + result.mi_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
